--- a/frontend/public/templates/mp_combined_dayahead_template.xlsx
+++ b/frontend/public/templates/mp_combined_dayahead_template.xlsx
@@ -1,370 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="REG" r:id="rId3" sheetId="1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REG" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="117">
-  <si>
-    <t>TYPE:</t>
-  </si>
-  <si>
-    <t>REG</t>
-  </si>
-  <si>
-    <t>DATE:</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>REVISION:</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>REASON:</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>Block Interval</t>
-  </si>
-  <si>
-    <t>5.1MW M/s SIRMOUR SMALL HYDRO POWER PVT LTD</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>M/s Physis Solar One Pvt Ltd Andad</t>
-  </si>
-  <si>
-    <t>M/s Physis Solar One Pvt Ltd Anjangaon</t>
-  </si>
-  <si>
-    <t>M/s Physis Solar One Pvt Ltd Ghughariyakhedi</t>
-  </si>
-  <si>
-    <t>M/s Physis Solar Power Two Pvt Ltd BALAKWADA</t>
-  </si>
-  <si>
-    <t>M/s Physis Solar Power Two Pvt Ltd BAMKHAL</t>
-  </si>
-  <si>
-    <t>M/s Physis Solar Power Two Pvt Ltd (NANDGAON)</t>
-  </si>
-  <si>
-    <t>M/s Physis Solar Power Two Pvt Ltd (SAWDA)</t>
-  </si>
-  <si>
-    <t>Availability</t>
-  </si>
-  <si>
-    <t>Forecast</t>
-  </si>
-  <si>
-    <t>00:00-00:15</t>
-  </si>
-  <si>
-    <t>00:15-00:30</t>
-  </si>
-  <si>
-    <t>00:30-00:45</t>
-  </si>
-  <si>
-    <t>00:45-01:00</t>
-  </si>
-  <si>
-    <t>01:00-01:15</t>
-  </si>
-  <si>
-    <t>01:15-01:30</t>
-  </si>
-  <si>
-    <t>01:30-01:45</t>
-  </si>
-  <si>
-    <t>01:45-02:00</t>
-  </si>
-  <si>
-    <t>02:00-02:15</t>
-  </si>
-  <si>
-    <t>02:15-02:30</t>
-  </si>
-  <si>
-    <t>02:30-02:45</t>
-  </si>
-  <si>
-    <t>02:45-03:00</t>
-  </si>
-  <si>
-    <t>03:00-03:15</t>
-  </si>
-  <si>
-    <t>03:15-03:30</t>
-  </si>
-  <si>
-    <t>03:30-03:45</t>
-  </si>
-  <si>
-    <t>03:45-04:00</t>
-  </si>
-  <si>
-    <t>04:00-04:15</t>
-  </si>
-  <si>
-    <t>04:15-04:30</t>
-  </si>
-  <si>
-    <t>04:30-04:45</t>
-  </si>
-  <si>
-    <t>04:45-05:00</t>
-  </si>
-  <si>
-    <t>05:00-05:15</t>
-  </si>
-  <si>
-    <t>05:15-05:30</t>
-  </si>
-  <si>
-    <t>05:30-05:45</t>
-  </si>
-  <si>
-    <t>05:45-06:00</t>
-  </si>
-  <si>
-    <t>06:00-06:15</t>
-  </si>
-  <si>
-    <t>06:15-06:30</t>
-  </si>
-  <si>
-    <t>06:30-06:45</t>
-  </si>
-  <si>
-    <t>06:45-07:00</t>
-  </si>
-  <si>
-    <t>07:00-07:15</t>
-  </si>
-  <si>
-    <t>07:15-07:30</t>
-  </si>
-  <si>
-    <t>07:30-07:45</t>
-  </si>
-  <si>
-    <t>07:45-08:00</t>
-  </si>
-  <si>
-    <t>08:00-08:15</t>
-  </si>
-  <si>
-    <t>08:15-08:30</t>
-  </si>
-  <si>
-    <t>08:30-08:45</t>
-  </si>
-  <si>
-    <t>08:45-09:00</t>
-  </si>
-  <si>
-    <t>09:00-09:15</t>
-  </si>
-  <si>
-    <t>09:15-09:30</t>
-  </si>
-  <si>
-    <t>09:30-09:45</t>
-  </si>
-  <si>
-    <t>09:45-10:00</t>
-  </si>
-  <si>
-    <t>10:00-10:15</t>
-  </si>
-  <si>
-    <t>10:15-10:30</t>
-  </si>
-  <si>
-    <t>10:30-10:45</t>
-  </si>
-  <si>
-    <t>10:45-11:00</t>
-  </si>
-  <si>
-    <t>11:00-11:15</t>
-  </si>
-  <si>
-    <t>11:15-11:30</t>
-  </si>
-  <si>
-    <t>11:30-11:45</t>
-  </si>
-  <si>
-    <t>11:45-12:00</t>
-  </si>
-  <si>
-    <t>12:00-12:15</t>
-  </si>
-  <si>
-    <t>12:15-12:30</t>
-  </si>
-  <si>
-    <t>12:30-12:45</t>
-  </si>
-  <si>
-    <t>12:45-13:00</t>
-  </si>
-  <si>
-    <t>13:00-13:15</t>
-  </si>
-  <si>
-    <t>13:15-13:30</t>
-  </si>
-  <si>
-    <t>13:30-13:45</t>
-  </si>
-  <si>
-    <t>13:45-14:00</t>
-  </si>
-  <si>
-    <t>14:00-14:15</t>
-  </si>
-  <si>
-    <t>14:15-14:30</t>
-  </si>
-  <si>
-    <t>14:30-14:45</t>
-  </si>
-  <si>
-    <t>14:45-15:00</t>
-  </si>
-  <si>
-    <t>15:00-15:15</t>
-  </si>
-  <si>
-    <t>15:15-15:30</t>
-  </si>
-  <si>
-    <t>15:30-15:45</t>
-  </si>
-  <si>
-    <t>15:45-16:00</t>
-  </si>
-  <si>
-    <t>16:00-16:15</t>
-  </si>
-  <si>
-    <t>16:15-16:30</t>
-  </si>
-  <si>
-    <t>16:30-16:45</t>
-  </si>
-  <si>
-    <t>16:45-17:00</t>
-  </si>
-  <si>
-    <t>17:00-17:15</t>
-  </si>
-  <si>
-    <t>17:15-17:30</t>
-  </si>
-  <si>
-    <t>17:30-17:45</t>
-  </si>
-  <si>
-    <t>17:45-18:00</t>
-  </si>
-  <si>
-    <t>18:00-18:15</t>
-  </si>
-  <si>
-    <t>18:15-18:30</t>
-  </si>
-  <si>
-    <t>18:30-18:45</t>
-  </si>
-  <si>
-    <t>18:45-19:00</t>
-  </si>
-  <si>
-    <t>19:00-19:15</t>
-  </si>
-  <si>
-    <t>19:15-19:30</t>
-  </si>
-  <si>
-    <t>19:30-19:45</t>
-  </si>
-  <si>
-    <t>19:45-20:00</t>
-  </si>
-  <si>
-    <t>20:00-20:15</t>
-  </si>
-  <si>
-    <t>20:15-20:30</t>
-  </si>
-  <si>
-    <t>20:30-20:45</t>
-  </si>
-  <si>
-    <t>20:45-21:00</t>
-  </si>
-  <si>
-    <t>21:00-21:15</t>
-  </si>
-  <si>
-    <t>21:15-21:30</t>
-  </si>
-  <si>
-    <t>21:30-21:45</t>
-  </si>
-  <si>
-    <t>21:45-22:00</t>
-  </si>
-  <si>
-    <t>22:00-22:15</t>
-  </si>
-  <si>
-    <t>22:15-22:30</t>
-  </si>
-  <si>
-    <t>22:30-22:45</t>
-  </si>
-  <si>
-    <t>22:45-23:00</t>
-  </si>
-  <si>
-    <t>23:00-23:15</t>
-  </si>
-  <si>
-    <t>23:15-23:30</t>
-  </si>
-  <si>
-    <t>23:30-23:45</t>
-  </si>
-  <si>
-    <t>23:45-24:00</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -372,18 +17,25 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <sz val="11.0"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
@@ -399,1458 +51,1928 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S102"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TYPE:</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>REG</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DATE:</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REVISION:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REASON:</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" t="s">
-        <v>11</v>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Block Interval</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5.1MW M/s SIRMOUR SMALL HYDRO POWER PVT LTD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar One Pvt Ltd Andad</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar One Pvt Ltd Anjangaon</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar One Pvt Ltd Ghughariyakhedi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar Power Two Pvt Ltd BALAKWADA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar Power Two Pvt Ltd BAMKHAL</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar Power Two Pvt Ltd (NANDGAON)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>M/s Physis Solar Power Two Pvt Ltd (SAWDA)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>MARUT_SHAKTI_CHANDWASA</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" t="s">
-        <v>20</v>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>00:00-00:15</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>00:15-00:30</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>00:30-00:45</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>00:45-01:00</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01:00-01:15</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01:15-01:30</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01:30-01:45</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01:45-02:00</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>02:00-02:15</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>02:15-02:30</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>02:30-02:45</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>02:45-03:00</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
+        <v>13</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03:00-03:15</t>
+        </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>03:15-03:30</t>
+        </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
+        <v>15</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>03:30-03:45</t>
+        </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
+        <v>16</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>03:45-04:00</t>
+        </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>04:00-04:15</t>
+        </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>04:15-04:30</t>
+        </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>04:30-04:45</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="B26" t="s">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>04:45-05:00</t>
+        </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="B27" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>05:00-05:15</t>
+        </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
+        <v>22</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>05:15-05:30</t>
+        </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
+        <v>23</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>05:30-05:45</t>
+        </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="B30" t="s">
-        <v>44</v>
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>05:45-06:00</t>
+        </is>
       </c>
       <c r="C30" t="n">
         <v>5.1</v>
@@ -1859,54 +1981,56 @@
         <v>0.01</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="B31" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>06:00-06:15</t>
+        </is>
       </c>
       <c r="C31" t="n">
         <v>5.1</v>
@@ -1939,7 +2063,7 @@
         <v>0.04</v>
       </c>
       <c r="M31" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
         <v>0.04</v>
@@ -1959,10 +2083,12 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>06:15-06:30</t>
+        </is>
       </c>
       <c r="C32" t="n">
         <v>5.1</v>
@@ -1995,7 +2121,7 @@
         <v>0.13</v>
       </c>
       <c r="M32" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
         <v>0.11</v>
@@ -2015,10 +2141,12 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
+        <v>27</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>06:30-06:45</t>
+        </is>
       </c>
       <c r="C33" t="n">
         <v>5.1</v>
@@ -2051,7 +2179,7 @@
         <v>0.21</v>
       </c>
       <c r="M33" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
         <v>0.18</v>
@@ -2071,10 +2199,12 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="B34" t="s">
-        <v>48</v>
+        <v>28</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>06:45-07:00</t>
+        </is>
       </c>
       <c r="C34" t="n">
         <v>5.1</v>
@@ -2107,7 +2237,7 @@
         <v>0.33</v>
       </c>
       <c r="M34" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
         <v>0.27</v>
@@ -2127,10 +2257,12 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07:00-07:15</t>
+        </is>
       </c>
       <c r="C35" t="n">
         <v>5.1</v>
@@ -2163,7 +2295,7 @@
         <v>0.52</v>
       </c>
       <c r="M35" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
         <v>0.42</v>
@@ -2183,10 +2315,12 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07:15-07:30</t>
+        </is>
       </c>
       <c r="C36" t="n">
         <v>5.1</v>
@@ -2219,7 +2353,7 @@
         <v>0.75</v>
       </c>
       <c r="M36" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
         <v>0.59</v>
@@ -2239,10 +2373,12 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="B37" t="s">
-        <v>51</v>
+        <v>31</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>07:30-07:45</t>
+        </is>
       </c>
       <c r="C37" t="n">
         <v>5.1</v>
@@ -2275,7 +2411,7 @@
         <v>0.98</v>
       </c>
       <c r="M37" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
         <v>0.78</v>
@@ -2295,10 +2431,12 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
+        <v>32</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>07:45-08:00</t>
+        </is>
       </c>
       <c r="C38" t="n">
         <v>5.1</v>
@@ -2331,7 +2469,7 @@
         <v>1.23</v>
       </c>
       <c r="M38" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
         <v>0.99</v>
@@ -2351,10 +2489,12 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
+        <v>33</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>08:00-08:15</t>
+        </is>
       </c>
       <c r="C39" t="n">
         <v>5.1</v>
@@ -2387,7 +2527,7 @@
         <v>1.49</v>
       </c>
       <c r="M39" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
         <v>1.21</v>
@@ -2407,10 +2547,12 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="B40" t="s">
-        <v>54</v>
+        <v>34</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>08:15-08:30</t>
+        </is>
       </c>
       <c r="C40" t="n">
         <v>5.1</v>
@@ -2422,7 +2564,7 @@
         <v>7.5</v>
       </c>
       <c r="F40" t="n">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>7.5</v>
@@ -2443,7 +2585,7 @@
         <v>1.76</v>
       </c>
       <c r="M40" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
         <v>1.45</v>
@@ -2458,15 +2600,17 @@
         <v>7.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
+        <v>35</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>08:30-08:45</t>
+        </is>
       </c>
       <c r="C41" t="n">
         <v>5.1</v>
@@ -2499,7 +2643,7 @@
         <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
         <v>1.61</v>
@@ -2519,10 +2663,12 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="B42" t="s">
-        <v>56</v>
+        <v>36</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>08:45-09:00</t>
+        </is>
       </c>
       <c r="C42" t="n">
         <v>5.1</v>
@@ -2555,7 +2701,7 @@
         <v>2.29</v>
       </c>
       <c r="M42" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
         <v>1.77</v>
@@ -2575,10 +2721,12 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>37.0</v>
-      </c>
-      <c r="B43" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>09:00-09:15</t>
+        </is>
       </c>
       <c r="C43" t="n">
         <v>5.1</v>
@@ -2611,7 +2759,7 @@
         <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
         <v>1.91</v>
@@ -2631,10 +2779,12 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="B44" t="s">
-        <v>58</v>
+        <v>38</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>09:15-09:30</t>
+        </is>
       </c>
       <c r="C44" t="n">
         <v>5.1</v>
@@ -2667,7 +2817,7 @@
         <v>2.8</v>
       </c>
       <c r="M44" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
         <v>2.04</v>
@@ -2687,10 +2837,12 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="B45" t="s">
-        <v>59</v>
+        <v>39</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>09:30-09:45</t>
+        </is>
       </c>
       <c r="C45" t="n">
         <v>5.1</v>
@@ -2723,7 +2875,7 @@
         <v>2.91</v>
       </c>
       <c r="M45" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
         <v>2.21</v>
@@ -2743,10 +2895,12 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="B46" t="s">
-        <v>60</v>
+        <v>40</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>09:45-10:00</t>
+        </is>
       </c>
       <c r="C46" t="n">
         <v>5.1</v>
@@ -2776,10 +2930,10 @@
         <v>7.5</v>
       </c>
       <c r="L46" t="n">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
         <v>2.38</v>
@@ -2799,10 +2953,12 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
+        <v>41</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
       </c>
       <c r="C47" t="n">
         <v>5.1</v>
@@ -2835,7 +2991,7 @@
         <v>3.05</v>
       </c>
       <c r="M47" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
         <v>2.53</v>
@@ -2855,10 +3011,12 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="B48" t="s">
-        <v>62</v>
+        <v>42</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10:15-10:30</t>
+        </is>
       </c>
       <c r="C48" t="n">
         <v>5.1</v>
@@ -2891,7 +3049,7 @@
         <v>3.06</v>
       </c>
       <c r="M48" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
         <v>2.66</v>
@@ -2911,10 +3069,12 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>63</v>
+        <v>43</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
       </c>
       <c r="C49" t="n">
         <v>5.1</v>
@@ -2947,7 +3107,7 @@
         <v>3.22</v>
       </c>
       <c r="M49" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
         <v>2.77</v>
@@ -2967,10 +3127,12 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>44.0</v>
-      </c>
-      <c r="B50" t="s">
-        <v>64</v>
+        <v>44</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
       </c>
       <c r="C50" t="n">
         <v>5.1</v>
@@ -3003,7 +3165,7 @@
         <v>3.36</v>
       </c>
       <c r="M50" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
         <v>2.87</v>
@@ -3023,10 +3185,12 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="B51" t="s">
-        <v>65</v>
+        <v>45</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>11:00-11:15</t>
+        </is>
       </c>
       <c r="C51" t="n">
         <v>5.1</v>
@@ -3059,7 +3223,7 @@
         <v>3.49</v>
       </c>
       <c r="M51" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
         <v>2.95</v>
@@ -3079,10 +3243,12 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="B52" t="s">
-        <v>66</v>
+        <v>46</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>11:15-11:30</t>
+        </is>
       </c>
       <c r="C52" t="n">
         <v>5.1</v>
@@ -3115,7 +3281,7 @@
         <v>3.61</v>
       </c>
       <c r="M52" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
         <v>3.02</v>
@@ -3135,10 +3301,12 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="B53" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11:30-11:45</t>
+        </is>
       </c>
       <c r="C53" t="n">
         <v>5.1</v>
@@ -3171,7 +3339,7 @@
         <v>3.74</v>
       </c>
       <c r="M53" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
         <v>3.03</v>
@@ -3191,10 +3359,12 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="B54" t="s">
-        <v>68</v>
+        <v>48</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11:45-12:00</t>
+        </is>
       </c>
       <c r="C54" t="n">
         <v>5.1</v>
@@ -3227,7 +3397,7 @@
         <v>3.85</v>
       </c>
       <c r="M54" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
         <v>3.03</v>
@@ -3247,10 +3417,12 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="B55" t="s">
-        <v>69</v>
+        <v>49</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
       </c>
       <c r="C55" t="n">
         <v>5.1</v>
@@ -3283,7 +3455,7 @@
         <v>3.94</v>
       </c>
       <c r="M55" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
         <v>3.01</v>
@@ -3303,10 +3475,12 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="B56" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
       </c>
       <c r="C56" t="n">
         <v>5.1</v>
@@ -3339,7 +3513,7 @@
         <v>4.01</v>
       </c>
       <c r="M56" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
         <v>2.98</v>
@@ -3359,10 +3533,12 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="B57" t="s">
-        <v>71</v>
+        <v>51</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
       </c>
       <c r="C57" t="n">
         <v>5.1</v>
@@ -3395,7 +3571,7 @@
         <v>3.93</v>
       </c>
       <c r="M57" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
         <v>3.03</v>
@@ -3415,10 +3591,12 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="B58" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12:45-13:00</t>
+        </is>
       </c>
       <c r="C58" t="n">
         <v>5.1</v>
@@ -3451,7 +3629,7 @@
         <v>3.82</v>
       </c>
       <c r="M58" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
         <v>3.08</v>
@@ -3471,10 +3649,12 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="B59" t="s">
-        <v>73</v>
+        <v>53</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>13:00-13:15</t>
+        </is>
       </c>
       <c r="C59" t="n">
         <v>5.1</v>
@@ -3507,7 +3687,7 @@
         <v>3.68</v>
       </c>
       <c r="M59" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
         <v>3.09</v>
@@ -3527,10 +3707,12 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>54.0</v>
-      </c>
-      <c r="B60" t="s">
-        <v>74</v>
+        <v>54</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>13:15-13:30</t>
+        </is>
       </c>
       <c r="C60" t="n">
         <v>5.1</v>
@@ -3563,7 +3745,7 @@
         <v>3.51</v>
       </c>
       <c r="M60" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
         <v>3.08</v>
@@ -3583,10 +3765,12 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="B61" t="s">
-        <v>75</v>
+        <v>55</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>13:30-13:45</t>
+        </is>
       </c>
       <c r="C61" t="n">
         <v>5.1</v>
@@ -3619,7 +3803,7 @@
         <v>3.48</v>
       </c>
       <c r="M61" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
         <v>2.98</v>
@@ -3639,10 +3823,12 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="B62" t="s">
-        <v>76</v>
+        <v>56</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>13:45-14:00</t>
+        </is>
       </c>
       <c r="C62" t="n">
         <v>5.1</v>
@@ -3675,7 +3861,7 @@
         <v>3.42</v>
       </c>
       <c r="M62" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
         <v>2.87</v>
@@ -3695,10 +3881,12 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>14:00-14:15</t>
+        </is>
       </c>
       <c r="C63" t="n">
         <v>5.1</v>
@@ -3731,7 +3919,7 @@
         <v>3.35</v>
       </c>
       <c r="M63" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
         <v>2.75</v>
@@ -3751,10 +3939,12 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="B64" t="s">
-        <v>78</v>
+        <v>58</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>14:15-14:30</t>
+        </is>
       </c>
       <c r="C64" t="n">
         <v>5.1</v>
@@ -3787,7 +3977,7 @@
         <v>3.26</v>
       </c>
       <c r="M64" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
         <v>2.61</v>
@@ -3807,10 +3997,12 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>59.0</v>
-      </c>
-      <c r="B65" t="s">
-        <v>79</v>
+        <v>59</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>14:30-14:45</t>
+        </is>
       </c>
       <c r="C65" t="n">
         <v>5.1</v>
@@ -3843,7 +4035,7 @@
         <v>3.05</v>
       </c>
       <c r="M65" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
         <v>2.48</v>
@@ -3863,10 +4055,12 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>60.0</v>
-      </c>
-      <c r="B66" t="s">
-        <v>80</v>
+        <v>60</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>14:45-15:00</t>
+        </is>
       </c>
       <c r="C66" t="n">
         <v>5.1</v>
@@ -3899,7 +4093,7 @@
         <v>2.85</v>
       </c>
       <c r="M66" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
         <v>2.35</v>
@@ -3919,10 +4113,12 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="B67" t="s">
-        <v>81</v>
+        <v>61</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>15:00-15:15</t>
+        </is>
       </c>
       <c r="C67" t="n">
         <v>5.1</v>
@@ -3955,7 +4151,7 @@
         <v>2.63</v>
       </c>
       <c r="M67" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>2.2</v>
@@ -3975,10 +4171,12 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="B68" t="s">
-        <v>82</v>
+        <v>62</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>15:15-15:30</t>
+        </is>
       </c>
       <c r="C68" t="n">
         <v>5.1</v>
@@ -4011,7 +4209,7 @@
         <v>2.4</v>
       </c>
       <c r="M68" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
         <v>2.05</v>
@@ -4031,10 +4229,12 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="B69" t="s">
-        <v>83</v>
+        <v>63</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>15:30-15:45</t>
+        </is>
       </c>
       <c r="C69" t="n">
         <v>5.1</v>
@@ -4067,7 +4267,7 @@
         <v>2.25</v>
       </c>
       <c r="M69" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
         <v>1.94</v>
@@ -4087,10 +4287,12 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>64.0</v>
-      </c>
-      <c r="B70" t="s">
-        <v>84</v>
+        <v>64</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>15:45-16:00</t>
+        </is>
       </c>
       <c r="C70" t="n">
         <v>5.1</v>
@@ -4123,7 +4325,7 @@
         <v>2.09</v>
       </c>
       <c r="M70" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
         <v>1.82</v>
@@ -4143,10 +4345,12 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>65.0</v>
-      </c>
-      <c r="B71" t="s">
-        <v>85</v>
+        <v>65</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>16:00-16:15</t>
+        </is>
       </c>
       <c r="C71" t="n">
         <v>5.1</v>
@@ -4179,7 +4383,7 @@
         <v>1.93</v>
       </c>
       <c r="M71" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
         <v>1.7</v>
@@ -4199,10 +4403,12 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66.0</v>
-      </c>
-      <c r="B72" t="s">
-        <v>86</v>
+        <v>66</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>16:15-16:30</t>
+        </is>
       </c>
       <c r="C72" t="n">
         <v>5.1</v>
@@ -4235,7 +4441,7 @@
         <v>1.76</v>
       </c>
       <c r="M72" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
         <v>1.56</v>
@@ -4255,10 +4461,12 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="B73" t="s">
-        <v>87</v>
+        <v>67</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>16:30-16:45</t>
+        </is>
       </c>
       <c r="C73" t="n">
         <v>5.1</v>
@@ -4291,7 +4499,7 @@
         <v>1.56</v>
       </c>
       <c r="M73" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N73" t="n">
         <v>1.33</v>
@@ -4311,10 +4519,12 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>68.0</v>
-      </c>
-      <c r="B74" t="s">
-        <v>88</v>
+        <v>68</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>16:45-17:00</t>
+        </is>
       </c>
       <c r="C74" t="n">
         <v>5.1</v>
@@ -4347,7 +4557,7 @@
         <v>1.36</v>
       </c>
       <c r="M74" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N74" t="n">
         <v>1.11</v>
@@ -4367,10 +4577,12 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>69.0</v>
-      </c>
-      <c r="B75" t="s">
-        <v>89</v>
+        <v>69</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>17:00-17:15</t>
+        </is>
       </c>
       <c r="C75" t="n">
         <v>5.1</v>
@@ -4403,7 +4615,7 @@
         <v>1.17</v>
       </c>
       <c r="M75" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N75" t="n">
         <v>0.91</v>
@@ -4423,10 +4635,12 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>70.0</v>
-      </c>
-      <c r="B76" t="s">
-        <v>90</v>
+        <v>70</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>17:15-17:30</t>
+        </is>
       </c>
       <c r="C76" t="n">
         <v>5.1</v>
@@ -4459,7 +4673,7 @@
         <v>0.98</v>
       </c>
       <c r="M76" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
         <v>0.72</v>
@@ -4479,10 +4693,12 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>71.0</v>
-      </c>
-      <c r="B77" t="s">
-        <v>91</v>
+        <v>71</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>17:30-17:45</t>
+        </is>
       </c>
       <c r="C77" t="n">
         <v>5.1</v>
@@ -4500,7 +4716,7 @@
         <v>7.5</v>
       </c>
       <c r="H77" t="n">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I77" t="n">
         <v>7.5</v>
@@ -4515,7 +4731,7 @@
         <v>0.75</v>
       </c>
       <c r="M77" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
         <v>0.58</v>
@@ -4535,10 +4751,12 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>72.0</v>
-      </c>
-      <c r="B78" t="s">
-        <v>92</v>
+        <v>72</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>17:45-18:00</t>
+        </is>
       </c>
       <c r="C78" t="n">
         <v>5.1</v>
@@ -4550,7 +4768,7 @@
         <v>7.5</v>
       </c>
       <c r="F78" t="n">
-        <v>0.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G78" t="n">
         <v>7.5</v>
@@ -4571,7 +4789,7 @@
         <v>0.53</v>
       </c>
       <c r="M78" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N78" t="n">
         <v>0.43</v>
@@ -4591,10 +4809,12 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>73.0</v>
-      </c>
-      <c r="B79" t="s">
-        <v>93</v>
+        <v>73</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>18:00-18:15</t>
+        </is>
       </c>
       <c r="C79" t="n">
         <v>5.1</v>
@@ -4627,7 +4847,7 @@
         <v>0.34</v>
       </c>
       <c r="M79" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N79" t="n">
         <v>0.29</v>
@@ -4647,10 +4867,12 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="B80" t="s">
-        <v>94</v>
+        <v>74</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>18:15-18:30</t>
+        </is>
       </c>
       <c r="C80" t="n">
         <v>5.1</v>
@@ -4683,7 +4905,7 @@
         <v>0.21</v>
       </c>
       <c r="M80" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N80" t="n">
         <v>0.18</v>
@@ -4703,10 +4925,12 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="B81" t="s">
-        <v>95</v>
+        <v>75</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>18:30-18:45</t>
+        </is>
       </c>
       <c r="C81" t="n">
         <v>5.1</v>
@@ -4739,7 +4963,7 @@
         <v>0.1</v>
       </c>
       <c r="M81" t="n">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N81" t="n">
         <v>0.09</v>
@@ -4759,10 +4983,12 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>76.0</v>
-      </c>
-      <c r="B82" t="s">
-        <v>96</v>
+        <v>76</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>18:45-19:00</t>
+        </is>
       </c>
       <c r="C82" t="n">
         <v>5.1</v>
@@ -4815,10 +5041,12 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>77.0</v>
-      </c>
-      <c r="B83" t="s">
-        <v>97</v>
+        <v>77</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>19:00-19:15</t>
+        </is>
       </c>
       <c r="C83" t="n">
         <v>5.1</v>
@@ -4827,1113 +5055,1151 @@
         <v>0.01</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>78.0</v>
-      </c>
-      <c r="B84" t="s">
-        <v>98</v>
+        <v>78</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>19:15-19:30</t>
+        </is>
       </c>
       <c r="C84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="B85" t="s">
-        <v>99</v>
+        <v>79</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>19:30-19:45</t>
+        </is>
       </c>
       <c r="C85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="B86" t="s">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>19:45-20:00</t>
+        </is>
       </c>
       <c r="C86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>81.0</v>
-      </c>
-      <c r="B87" t="s">
-        <v>101</v>
+        <v>81</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>20:00-20:15</t>
+        </is>
       </c>
       <c r="C87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>82.0</v>
-      </c>
-      <c r="B88" t="s">
-        <v>102</v>
+        <v>82</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>20:15-20:30</t>
+        </is>
       </c>
       <c r="C88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="B89" t="s">
-        <v>103</v>
+        <v>83</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>20:30-20:45</t>
+        </is>
       </c>
       <c r="C89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>84.0</v>
-      </c>
-      <c r="B90" t="s">
-        <v>104</v>
+        <v>84</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20:45-21:00</t>
+        </is>
       </c>
       <c r="C90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="B91" t="s">
-        <v>105</v>
+        <v>85</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>21:00-21:15</t>
+        </is>
       </c>
       <c r="C91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="B92" t="s">
-        <v>106</v>
+        <v>86</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>21:15-21:30</t>
+        </is>
       </c>
       <c r="C92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>87.0</v>
-      </c>
-      <c r="B93" t="s">
-        <v>107</v>
+        <v>87</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>21:30-21:45</t>
+        </is>
       </c>
       <c r="C93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>88.0</v>
-      </c>
-      <c r="B94" t="s">
-        <v>108</v>
+        <v>88</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>21:45-22:00</t>
+        </is>
       </c>
       <c r="C94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="B95" t="s">
-        <v>109</v>
+        <v>89</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>22:00-22:15</t>
+        </is>
       </c>
       <c r="C95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>90.0</v>
-      </c>
-      <c r="B96" t="s">
-        <v>110</v>
+        <v>90</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>22:15-22:30</t>
+        </is>
       </c>
       <c r="C96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>91.0</v>
-      </c>
-      <c r="B97" t="s">
-        <v>111</v>
+        <v>91</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>22:30-22:45</t>
+        </is>
       </c>
       <c r="C97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>92.0</v>
-      </c>
-      <c r="B98" t="s">
-        <v>112</v>
+        <v>92</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>22:45-23:00</t>
+        </is>
       </c>
       <c r="C98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>93.0</v>
-      </c>
-      <c r="B99" t="s">
-        <v>113</v>
+        <v>93</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>23:00-23:15</t>
+        </is>
       </c>
       <c r="C99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>94.0</v>
-      </c>
-      <c r="B100" t="s">
-        <v>114</v>
+        <v>94</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>23:15-23:30</t>
+        </is>
       </c>
       <c r="C100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="B101" t="s">
-        <v>115</v>
+        <v>95</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>23:30-23:45</t>
+        </is>
       </c>
       <c r="C101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>96.0</v>
-      </c>
-      <c r="B102" t="s">
-        <v>116</v>
+        <v>96</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>23:45-24:00</t>
+        </is>
       </c>
       <c r="C102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>